--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Laja</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Nacimiento</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Bárbara</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:41</t>
+    <t xml:space="preserve">2026-10-04 09:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:02</t>
+    <t xml:space="preserve">2026-10-05 10:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -903,7 +903,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>267362.62</v>
+        <v>267362.63</v>
       </c>
     </row>
     <row r="22">
